--- a/artfynd/A 39973-2025 artfynd.xlsx
+++ b/artfynd/A 39973-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118640157</v>
+        <v>119286453</v>
       </c>
       <c r="B2" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stugu-sättsjön, Jmt</t>
+          <t>Tjärnbergen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533326</v>
+        <v>533182</v>
       </c>
       <c r="R2" t="n">
-        <v>6999332</v>
+        <v>6999249</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118640148</v>
+        <v>119286459</v>
       </c>
       <c r="B3" t="n">
-        <v>78230</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533243</v>
+        <v>533258</v>
       </c>
       <c r="R3" t="n">
-        <v>6999244</v>
+        <v>6999298</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118640151</v>
+        <v>119286462</v>
       </c>
       <c r="B4" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjärnbergen, Jmt</t>
+          <t>Stugu-sättsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533254</v>
+        <v>533326</v>
       </c>
       <c r="R4" t="n">
-        <v>6999234</v>
+        <v>6999332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118640143</v>
+        <v>119286452</v>
       </c>
       <c r="B5" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118640145</v>
+        <v>119286461</v>
       </c>
       <c r="B6" t="n">
-        <v>90533</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533182</v>
+        <v>533326</v>
       </c>
       <c r="R6" t="n">
-        <v>6999249</v>
+        <v>6999332</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118640153</v>
+        <v>119286454</v>
       </c>
       <c r="B7" t="n">
-        <v>79111</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533258</v>
+        <v>533179</v>
       </c>
       <c r="R7" t="n">
-        <v>6999298</v>
+        <v>6999279</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118640152</v>
+        <v>119286455</v>
       </c>
       <c r="B8" t="n">
-        <v>78230</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533260</v>
+        <v>533243</v>
       </c>
       <c r="R8" t="n">
-        <v>6999317</v>
+        <v>6999244</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118640154</v>
+        <v>119286458</v>
       </c>
       <c r="B9" t="n">
-        <v>78230</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533258</v>
+        <v>533260</v>
       </c>
       <c r="R9" t="n">
-        <v>6999298</v>
+        <v>6999317</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118640147</v>
+        <v>119286460</v>
       </c>
       <c r="B10" t="n">
-        <v>78230</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533179</v>
+        <v>533258</v>
       </c>
       <c r="R10" t="n">
-        <v>6999279</v>
+        <v>6999298</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,210 +1545,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>118640149</v>
-      </c>
-      <c r="B11" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tjärnbergen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>533211</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6999160</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Stugun</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Noel Wieser</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Noel Wieser</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>118640155</v>
-      </c>
-      <c r="B12" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Tjärnbergen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>533326</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6999332</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Stugun</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Noel Wieser</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Noel Wieser</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39973-2025 artfynd.xlsx
+++ b/artfynd/A 39973-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286453</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286459</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286462</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286452</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286461</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286454</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286455</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286458</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286460</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>